--- a/astro-site/public/dl/guia-chocolateria-obrador/vida-util-rellenos-y-rotacion.xlsx
+++ b/astro-site/public/dl/guia-chocolateria-obrador/vida-util-rellenos-y-rotacion.xlsx
@@ -6242,7 +6242,7 @@
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>kit-tareas-chocolateria/08-apertura-cierre-negocio.xlsx!Apertura del Negocio</t>
+          <t>kit-tareas-chocolateria/08-apertura-cierre-negocio.xlsx, hoja «Apertura del Negocio»</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>kit-tareas-chocolateria/01-apertura-cierre.xlsx!Apertura</t>
+          <t>kit-tareas-chocolateria/01-apertura-cierre.xlsx, hoja «Apertura»</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>kit-tareas-chocolateria/01-apertura-cierre.xlsx!Apertura</t>
+          <t>kit-tareas-chocolateria/01-apertura-cierre.xlsx, hoja «Apertura»</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -6323,7 +6323,7 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>kit-tareas-chocolateria/01-apertura-cierre.xlsx!Apertura</t>
+          <t>kit-tareas-chocolateria/01-apertura-cierre.xlsx, hoja «Apertura»</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>kit-tareas-chocolateria/08-apertura-cierre-negocio.xlsx!Apertura del Negocio</t>
+          <t>kit-tareas-chocolateria/08-apertura-cierre-negocio.xlsx, hoja «Apertura del Negocio»</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">

--- a/astro-site/public/dl/guia-chocolateria-obrador/vida-util-rellenos-y-rotacion.xlsx
+++ b/astro-site/public/dl/guia-chocolateria-obrador/vida-util-rellenos-y-rotacion.xlsx
@@ -973,7 +973,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Clientes por dia en velocidad de crucero. NO es un dato del sector: `N-13` prohibe publicar un ticket medio de chocolateria o un reparto mensual de ventas como dato, porque no existe dato publico. La guia ensena a medirlo con el TPV en dos semanas. Esta calibrado para que el margen neto del ano de crucero caiga entre el 9 % y el 11 %: por encima, el caso se lee como optimista y un refutador lo tumba con razon. Es la UNICA palanca que se toca para mover el margen; los costes no se maquillan.</t>
+          <t>Clientes por día en velocidad de crucero. NO es un dato del sector: `N-13` prohíbe publicar un ticket medio de chocolatería o un reparto mensual de ventas como dato, porque no existe dato publico. La guía enseña a medirlo con el TPV en dos semanas. Esta calibrado para que el margen neto del año de crucero caiga entre el 9 % y el 11 %: por encima, el caso se lee como optimista y un refutador lo tumba con razón. Es la ÚNICA palanca que se toca para mover el margen; los costes no se maquillan.</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>De aqui sale el ticket medio, que NO se teclea: se calcula como PVP medio ponderado de la carta x piezas por ticket. En bomboneria es BAJO -1,4- porque la unidad de venta real es la caja, no la pieza: quien entra a por un regalo se lleva UNA caja de 20 euros, no ocho bombones sueltos.</t>
+          <t>De aquí sale el ticket medio, que NO se teclea: se calcula como PVP medio ponderado de la carta x piezas por ticket. En bombonería es BAJO -1,4- porque la unidad de venta real es la caja, no la pieza: quien entra a por un regalo se lleva UNA caja de 20 euros, no ocho bombones sueltos.</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>6 dias por semana x 52 semanas = 312, menos 8 dias de cierre por festivos = 304. En agosto la TIENDA NO CIERRA: lo que para es el obrador (D36, y el literal del kit dice «la tienda abre para el turista aunque el obrador pare»). Una bomboneria de menos de 300 m2 tiene libertad horaria por el art. 5.2 de la Ley 1/2004, no por el 5.1 (`CHN-77`).</t>
+          <t>6 días por semana x 52 semanas = 312, menos 8 días de cierre por festivos = 304. En agosto la TIENDA NO CIERRA: lo que para es el obrador (D36, y el literal del kit dice «la tienda abre para el turista aunque el obrador pare»). Una bombonería de menos de 300 m² tiene libertad horaria por el art. 5.2 de la Ley 1/2004, no por el 5.1 (`CHN-77`).</t>
         </is>
       </c>
     </row>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>Es el punto en el que la manteca de cacao empieza a fundir, y el que publica el kit en su hoja de apertura. El semáforo de la vitrina SÓLO se enciende por encima de este número: los 16-18 grados C de objetivo del propio kit no se ponen nunca en rojo.</t>
+          <t>Es el punto en el que la manteca de cacao empieza a fundir, y el que publica el kit en su hoja de apertura. El semáforo de la vitrina SÓLO se enciende por encima de este número: los 16-18 °C de objetivo del propio kit no se ponen nunca en rojo.</t>
         </is>
       </c>
     </row>
@@ -1372,12 +1372,12 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Bombon de ganache de chocolate negro 70 %</t>
+          <t>Bombón de ganache de chocolate negro 70 %</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bombones de coleccion</t>
+          <t>Bombones de colección</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>10-15 dias</t>
+          <t>10-15 días</t>
         </is>
       </c>
       <c r="I16" t="str">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>Actividad de agua alta: en refrigeracion a 0-4 grados C y atemperar CERRADOS antes de abrir, o condensan</t>
+          <t>Actividad de agua alta: en refrigeración a 0-4 °C y atemperar CERRADOS antes de abrir, o condensan</t>
         </is>
       </c>
     </row>
@@ -1421,12 +1421,12 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Bombon de ganache de leche y vainilla</t>
+          <t>Bombón de ganache de leche y vainilla</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bombones de coleccion</t>
+          <t>Bombones de colección</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
@@ -1470,12 +1470,12 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Bombon de praline de avellana</t>
+          <t>Bombón de praline de avellana</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bombones de coleccion</t>
+          <t>Bombones de colección</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>La grasa del fruto seco se enrancia y el frio no lo evita: manda la fecha, no el aspecto</t>
+          <t>La grasa del fruto seco se enrancia y el frío no lo evita: manda la fecha, no el aspecto</t>
         </is>
       </c>
     </row>
@@ -1519,12 +1519,12 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Bombon de gianduja de avellana</t>
+          <t>Bombón de gianduja de avellana</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bombones de coleccion</t>
+          <t>Bombones de colección</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>La grasa del fruto seco se enrancia y el frio no lo evita: manda la fecha, no el aspecto</t>
+          <t>La grasa del fruto seco se enrancia y el frío no lo evita: manda la fecha, no el aspecto</t>
         </is>
       </c>
     </row>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bombones de coleccion</t>
+          <t>Bombones de colección</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Bombon de licor de ron</t>
+          <t>Bombón de licor de ron</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bombones de coleccion</t>
+          <t>Bombones de colección</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>Vigilar la cristalizacion del azucar en la cascara: revienta y gotea</t>
+          <t>Vigilar la cristalización del azúcar en la cascara: revienta y gotea</t>
         </is>
       </c>
     </row>
@@ -1666,12 +1666,12 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Bombon de caramelo salado</t>
+          <t>Bombón de caramelo salado</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bombones de coleccion</t>
+          <t>Bombones de colección</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Bombon de praline de cacahuete</t>
+          <t>Bombón de praline de cacahuete</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bombones de coleccion</t>
+          <t>Bombones de colección</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>La grasa del fruto seco se enrancia y el frio no lo evita: manda la fecha, no el aspecto</t>
+          <t>La grasa del fruto seco se enrancia y el frío no lo evita: manda la fecha, no el aspecto</t>
         </is>
       </c>
     </row>
@@ -1764,12 +1764,12 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Bombon crujiente de sesamo y barquillo</t>
+          <t>Bombón crujiente de sesamo y barquillo</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bombones de coleccion</t>
+          <t>Bombones de colección</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
@@ -1813,12 +1813,12 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Bombon de naranja confitada y chocolate negro</t>
+          <t>Bombón de naranja confitada y chocolate negro</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bombones de coleccion</t>
+          <t>Bombones de colección</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>La grasa del fruto seco se enrancia y el frio no lo evita: manda la fecha, no el aspecto</t>
+          <t>La grasa del fruto seco se enrancia y el frío no lo evita: manda la fecha, no el aspecto</t>
         </is>
       </c>
     </row>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>Masa de chocolate a la taza (azucar, cacao desgrasado y almidon)</t>
+          <t>Masa de chocolate a la taza (azúcar, cacao desgrasado y almidón)</t>
         </is>
       </c>
       <c r="E32" s="11" t="n">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>Masa de chocolate a la taza (azucar, cacao desgrasado y almidon)</t>
+          <t>Masa de chocolate a la taza (azúcar, cacao desgrasado y almidón)</t>
         </is>
       </c>
       <c r="E33" s="11" t="n">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>Masa de chocolate a la taza (azucar, cacao desgrasado y almidon)</t>
+          <t>Masa de chocolate a la taza (azúcar, cacao desgrasado y almidón)</t>
         </is>
       </c>
       <c r="E34" s="11" t="n">
@@ -2429,7 +2429,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>10-15 dias</t>
+          <t>10-15 días</t>
         </is>
       </c>
       <c r="I37" t="str">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>Actividad de agua alta: en refrigeracion a 0-4 grados C y atemperar CERRADOS antes de abrir, o condensan</t>
+          <t>Actividad de agua alta: en refrigeración a 0-4 °C y atemperar CERRADOS antes de abrir, o condensan</t>
         </is>
       </c>
     </row>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Turron de chocolate con almendra, 250 g</t>
+          <t>Turrón de chocolate con almendra, 250 g</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>Bombones de ganache con nata UHT, sorbato o alcohol</t>
+          <t>Bombones de ganache con nata fresca</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>4-8 semanas</t>
+          <t>10-15 días</t>
         </is>
       </c>
       <c r="I40" t="str">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="J40" s="6" t="inlineStr">
         <is>
-          <t>El conservante y el alcohol bajan la actividad de agua; sin ellos no se llega ni a la mitad</t>
+          <t>Actividad de agua alta: en refrigeración a 0-4 °C y atemperar CERRADOS antes de abrir, o condensan</t>
         </is>
       </c>
     </row>
@@ -2620,12 +2620,12 @@
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>Bombones de ganache con nata UHT, sorbato o alcohol</t>
+          <t>Bombones de ganache con nata fresca</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>4-8 semanas</t>
+          <t>10-15 días</t>
         </is>
       </c>
       <c r="I41" t="str">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>El conservante y el alcohol bajan la actividad de agua; sin ellos no se llega ni a la mitad</t>
+          <t>Actividad de agua alta: en refrigeración a 0-4 °C y atemperar CERRADOS antes de abrir, o condensan</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>Bombones de ganache con nata UHT, sorbato o alcohol</t>
+          <t>Bombones de ganache con nata fresca</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>4-8 semanas</t>
+          <t>10-15 días</t>
         </is>
       </c>
       <c r="I42" t="str">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="J42" s="6" t="inlineStr">
         <is>
-          <t>El conservante y el alcohol bajan la actividad de agua; sin ellos no se llega ni a la mitad</t>
+          <t>Actividad de agua alta: en refrigeración a 0-4 °C y atemperar CERRADOS antes de abrir, o condensan</t>
         </is>
       </c>
     </row>
@@ -2718,12 +2718,12 @@
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>Bombones de ganache con nata UHT, sorbato o alcohol</t>
+          <t>Bombones de ganache con nata fresca</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>4-8 semanas</t>
+          <t>10-15 días</t>
         </is>
       </c>
       <c r="I43" t="str">
@@ -2732,7 +2732,7 @@
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
-          <t>El conservante y el alcohol bajan la actividad de agua; sin ellos no se llega ni a la mitad</t>
+          <t>Actividad de agua alta: en refrigeración a 0-4 °C y atemperar CERRADOS antes de abrir, o condensan</t>
         </is>
       </c>
     </row>
@@ -2895,7 +2895,7 @@
     <row r="6" ht="46" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Los diez plazos de abajo son los del Kit de Tareas Chocolatería, fichero 02-partidas-produccion.xlsx, hoja Moldeado, tabla «vida útil y conservación orientativas a 15-18 grados C y 50-60 % de humedad». Son ORIENTATIVOS y de la casa, no de una norma: ninguna norma publica la vida útil del chocolate. La equivalencia en días de la columna E y F es aritmética nuestra -el kit escribe «4-8 semanas»- y está para que el semáforo pueda comparar.</t>
+          <t>Los diez plazos de abajo son los del Kit de Tareas Chocolatería, fichero 02-partidas-produccion.xlsx, hoja Moldeado, tabla «vida útil y conservación orientativas a 15-18 °C y 50-60 % de humedad». Son ORIENTATIVOS y de la casa, no de una norma: ninguna norma publica la vida útil del chocolate. La equivalencia en días de la columna E y F es aritmética nuestra -el kit escribe «4-8 semanas»- y está para que el semáforo pueda comparar.</t>
         </is>
       </c>
     </row>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Bombon de ganache de chocolate negro 70 %</t>
+          <t>Bombón de ganache de chocolate negro 70 %</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>10-15 dias</t>
+          <t>10-15 días</t>
         </is>
       </c>
       <c r="E16" s="10" t="n">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Bombon de ganache de leche y vainilla</t>
+          <t>Bombón de ganache de leche y vainilla</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Bombon de praline de avellana</t>
+          <t>Bombón de praline de avellana</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Bombon de gianduja de avellana</t>
+          <t>Bombón de gianduja de avellana</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Bombon de licor de ron</t>
+          <t>Bombón de licor de ron</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Bombon de caramelo salado</t>
+          <t>Bombón de caramelo salado</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Bombon de praline de cacahuete</t>
+          <t>Bombón de praline de cacahuete</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Bombon crujiente de sesamo y barquillo</t>
+          <t>Bombón crujiente de sesamo y barquillo</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Bombon de naranja confitada y chocolate negro</t>
+          <t>Bombón de naranja confitada y chocolate negro</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
@@ -4063,7 +4063,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>10-15 dias</t>
+          <t>10-15 días</t>
         </is>
       </c>
       <c r="E37" s="10" t="n">
@@ -4104,7 +4104,7 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Turron de chocolate con almendra, 250 g</t>
+          <t>Turrón de chocolate con almendra, 250 g</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>10-15 dias</t>
+          <t>10-15 días</t>
         </is>
       </c>
       <c r="E40" s="10" t="n">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>10-15 dias</t>
+          <t>10-15 días</t>
         </is>
       </c>
       <c r="E41" s="10" t="n">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>10-15 dias</t>
+          <t>10-15 días</t>
         </is>
       </c>
       <c r="E42" s="10" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>10-15 dias</t>
+          <t>10-15 días</t>
         </is>
       </c>
       <c r="E43" s="10" t="n">
@@ -4510,12 +4510,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>10-15 dias</t>
+          <t>10-15 días</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>Actividad de agua alta: en refrigeracion a 0-4 grados C y atemperar CERRADOS antes de abrir, o condensan</t>
+          <t>Actividad de agua alta: en refrigeración a 0-4 °C y atemperar CERRADOS antes de abrir, o condensan</t>
         </is>
       </c>
     </row>
@@ -4549,7 +4549,7 @@
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>La grasa del fruto seco se enrancia y el frio no lo evita: manda la fecha, no el aspecto</t>
+          <t>La grasa del fruto seco se enrancia y el frío no lo evita: manda la fecha, no el aspecto</t>
         </is>
       </c>
     </row>
@@ -4583,7 +4583,7 @@
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>Vigilar la cristalizacion del azucar en la cascara: revienta y gotea</t>
+          <t>Vigilar la cristalización del azúcar en la cascara: revienta y gotea</t>
         </is>
       </c>
     </row>
@@ -4634,14 +4634,14 @@
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>Al descongelar condensa, el agua disuelve el azucar de la superficie y deja sugar bloom. Solo el granel de ganache admite -18 grados C 1-2 meses, descongelado 24 h en camara y sin abrir</t>
+          <t>Al descongelar condensa, el agua disuelve el azúcar de la superficie y deja sugar bloom. Solo el granel de ganache admite -18 °C 1-2 meses, descongelado 24 h en cámara y sin abrir</t>
         </is>
       </c>
     </row>
     <row r="58" ht="34" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Fuente: kit-tareas-chocolateria/02-partidas-produccion.xlsx!Moldeado. La última fila no es un plazo: es una prohibición. El chocolate acabado NO se congela; al descongelar condensa, el agua disuelve el azúcar de la superficie y deja velo. Sólo el granel de ganache admite frío negativo, y con condiciones.</t>
+          <t>Fuente: kit-tareas-chocolateria/02-partidas-produccion.xlsx, hoja «Moldeado». La última fila no es un plazo: es una prohibición. El chocolate acabado NO se congela; al descongelar condensa, el agua disuelve el azúcar de la superficie y deja velo. Sólo el granel de ganache admite frío negativo, y con condiciones.</t>
         </is>
       </c>
     </row>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservacion POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran ademas las doce menciones del art. 9.1 del Rgto. 1169/2011 (`CHN-35`) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (`CHN-36`).</t>
+          <t>Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservación POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran además las doce menciones del art. 9.1 del Rgto. 1169/2011 (`CHN-35`) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (`CHN-36`).</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Se despacha a granel en la vitrina, sin etiqueta. Entonces la referencia NO es el art. 4.2: es TU sistema de autocontrol, y la temperatura y la vida util las declaras tu y constan en el (`CHN-30`, y `CHN-87`: «chocolate», «cacao», «bombon» y «confiteria» aparecen 0 veces en todo el RD 1021/2022). Los alergenos pueden ir en cartel (`CHN-89`) y el lote tiene tres vias de exencion (`CHN-36`).</t>
+          <t>Se despacha a granel en la vitrina, sin etiqueta. Entonces la referencia NO es el art. 4.2: es TU sistema de autocontrol, y la temperatura y la vida útil las declaras tu y constan en el (`CHN-30`, y `CHN-87`: «chocolate», «cacao», «bombón» y «confitería» aparecen 0 veces en todo el RD 1021/2022). Los alérgenos pueden ir en cartel (`CHN-89`) y el lote tiene tres vías de exención (`CHN-36`).</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Bombon de ganache de chocolate negro 70 %</t>
+          <t>Bombón de ganache de chocolate negro 70 %</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="E16" t="str">
         <f>IF($C16=$A$8,$B$8,"")</f>
-        <v>Se despacha a granel en la vitrina, sin etiqueta. Entonces la referencia NO es el art. 4.2: es TU sistema de autocontrol, y la temperatura y la vida util las declaras tu y constan en el (`CHN-30`, y `CHN-87`: «chocolate», «cacao», «bombon» y «confiteria» aparecen 0 veces en todo el RD 1021/2022). Los alergenos pueden ir en cartel (`CHN-89`) y el lote tiene tres vias de exencion (`CHN-36`).</v>
+        <v>Se despacha a granel en la vitrina, sin etiqueta. Entonces la referencia NO es el art. 4.2: es TU sistema de autocontrol, y la temperatura y la vida útil las declaras tu y constan en el (`CHN-30`, y `CHN-87`: «chocolate», «cacao», «bombón» y «confitería» aparecen 0 veces en todo el RD 1021/2022). Los alérgenos pueden ir en cartel (`CHN-89`) y el lote tiene tres vías de exención (`CHN-36`).</v>
       </c>
       <c r="F16" t="str">
         <f>IF($C16=$A$7,$F$7,IF($C16=$A$8,$F$8,""))</f>
@@ -4945,7 +4945,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Bombon de ganache de leche y vainilla</t>
+          <t>Bombón de ganache de leche y vainilla</t>
         </is>
       </c>
       <c r="C17" s="14" t="inlineStr">
@@ -4959,7 +4959,7 @@
       </c>
       <c r="E17" t="str">
         <f>IF($C17=$A$8,$B$8,"")</f>
-        <v>Se despacha a granel en la vitrina, sin etiqueta. Entonces la referencia NO es el art. 4.2: es TU sistema de autocontrol, y la temperatura y la vida util las declaras tu y constan en el (`CHN-30`, y `CHN-87`: «chocolate», «cacao», «bombon» y «confiteria» aparecen 0 veces en todo el RD 1021/2022). Los alergenos pueden ir en cartel (`CHN-89`) y el lote tiene tres vias de exencion (`CHN-36`).</v>
+        <v>Se despacha a granel en la vitrina, sin etiqueta. Entonces la referencia NO es el art. 4.2: es TU sistema de autocontrol, y la temperatura y la vida útil las declaras tu y constan en el (`CHN-30`, y `CHN-87`: «chocolate», «cacao», «bombón» y «confitería» aparecen 0 veces en todo el RD 1021/2022). Los alérgenos pueden ir en cartel (`CHN-89`) y el lote tiene tres vías de exención (`CHN-36`).</v>
       </c>
       <c r="F17" t="str">
         <f>IF($C17=$A$7,$F$7,IF($C17=$A$8,$F$8,""))</f>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Bombon de praline de avellana</t>
+          <t>Bombón de praline de avellana</t>
         </is>
       </c>
       <c r="C18" s="14" t="inlineStr">
@@ -5000,7 +5000,7 @@
       </c>
       <c r="E18" t="str">
         <f>IF($C18=$A$8,$B$8,"")</f>
-        <v>Se despacha a granel en la vitrina, sin etiqueta. Entonces la referencia NO es el art. 4.2: es TU sistema de autocontrol, y la temperatura y la vida util las declaras tu y constan en el (`CHN-30`, y `CHN-87`: «chocolate», «cacao», «bombon» y «confiteria» aparecen 0 veces en todo el RD 1021/2022). Los alergenos pueden ir en cartel (`CHN-89`) y el lote tiene tres vias de exencion (`CHN-36`).</v>
+        <v>Se despacha a granel en la vitrina, sin etiqueta. Entonces la referencia NO es el art. 4.2: es TU sistema de autocontrol, y la temperatura y la vida útil las declaras tu y constan en el (`CHN-30`, y `CHN-87`: «chocolate», «cacao», «bombón» y «confitería» aparecen 0 veces en todo el RD 1021/2022). Los alérgenos pueden ir en cartel (`CHN-89`) y el lote tiene tres vías de exención (`CHN-36`).</v>
       </c>
       <c r="F18" t="str">
         <f>IF($C18=$A$7,$F$7,IF($C18=$A$8,$F$8,""))</f>
@@ -5027,7 +5027,7 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Bombon de gianduja de avellana</t>
+          <t>Bombón de gianduja de avellana</t>
         </is>
       </c>
       <c r="C19" s="14" t="inlineStr">
@@ -5041,7 +5041,7 @@
       </c>
       <c r="E19" t="str">
         <f>IF($C19=$A$8,$B$8,"")</f>
-        <v>Se despacha a granel en la vitrina, sin etiqueta. Entonces la referencia NO es el art. 4.2: es TU sistema de autocontrol, y la temperatura y la vida util las declaras tu y constan en el (`CHN-30`, y `CHN-87`: «chocolate», «cacao», «bombon» y «confiteria» aparecen 0 veces en todo el RD 1021/2022). Los alergenos pueden ir en cartel (`CHN-89`) y el lote tiene tres vias de exencion (`CHN-36`).</v>
+        <v>Se despacha a granel en la vitrina, sin etiqueta. Entonces la referencia NO es el art. 4.2: es TU sistema de autocontrol, y la temperatura y la vida útil las declaras tu y constan en el (`CHN-30`, y `CHN-87`: «chocolate», «cacao», «bombón» y «confitería» aparecen 0 veces en todo el RD 1021/2022). Los alérgenos pueden ir en cartel (`CHN-89`) y el lote tiene tres vías de exención (`CHN-36`).</v>
       </c>
       <c r="F19" t="str">
         <f>IF($C19=$A$7,$F$7,IF($C19=$A$8,$F$8,""))</f>
@@ -5082,7 +5082,7 @@
       </c>
       <c r="E20" t="str">
         <f>IF($C20=$A$8,$B$8,"")</f>
-        <v>Se despacha a granel en la vitrina, sin etiqueta. Entonces la referencia NO es el art. 4.2: es TU sistema de autocontrol, y la temperatura y la vida util las declaras tu y constan en el (`CHN-30`, y `CHN-87`: «chocolate», «cacao», «bombon» y «confiteria» aparecen 0 veces en todo el RD 1021/2022). Los alergenos pueden ir en cartel (`CHN-89`) y el lote tiene tres vias de exencion (`CHN-36`).</v>
+        <v>Se despacha a granel en la vitrina, sin etiqueta. Entonces la referencia NO es el art. 4.2: es TU sistema de autocontrol, y la temperatura y la vida útil las declaras tu y constan en el (`CHN-30`, y `CHN-87`: «chocolate», «cacao», «bombón» y «confitería» aparecen 0 veces en todo el RD 1021/2022). Los alérgenos pueden ir en cartel (`CHN-89`) y el lote tiene tres vías de exención (`CHN-36`).</v>
       </c>
       <c r="F20" t="str">
         <f>IF($C20=$A$7,$F$7,IF($C20=$A$8,$F$8,""))</f>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Bombon de licor de ron</t>
+          <t>Bombón de licor de ron</t>
         </is>
       </c>
       <c r="C21" s="14" t="inlineStr">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="E21" t="str">
         <f>IF($C21=$A$8,$B$8,"")</f>
-        <v>Se despacha a granel en la vitrina, sin etiqueta. Entonces la referencia NO es el art. 4.2: es TU sistema de autocontrol, y la temperatura y la vida util las declaras tu y constan en el (`CHN-30`, y `CHN-87`: «chocolate», «cacao», «bombon» y «confiteria» aparecen 0 veces en todo el RD 1021/2022). Los alergenos pueden ir en cartel (`CHN-89`) y el lote tiene tres vias de exencion (`CHN-36`).</v>
+        <v>Se despacha a granel en la vitrina, sin etiqueta. Entonces la referencia NO es el art. 4.2: es TU sistema de autocontrol, y la temperatura y la vida útil las declaras tu y constan en el (`CHN-30`, y `CHN-87`: «chocolate», «cacao», «bombón» y «confitería» aparecen 0 veces en todo el RD 1021/2022). Los alérgenos pueden ir en cartel (`CHN-89`) y el lote tiene tres vías de exención (`CHN-36`).</v>
       </c>
       <c r="F21" t="str">
         <f>IF($C21=$A$7,$F$7,IF($C21=$A$8,$F$8,""))</f>
@@ -5150,7 +5150,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Bombon de caramelo salado</t>
+          <t>Bombón de caramelo salado</t>
         </is>
       </c>
       <c r="C22" s="14" t="inlineStr">
@@ -5164,7 +5164,7 @@
       </c>
       <c r="E22" t="str">
         <f>IF($C22=$A$8,$B$8,"")</f>
-        <v>Se despacha a granel en la vitrina, sin etiqueta. Entonces la referencia NO es el art. 4.2: es TU sistema de autocontrol, y la temperatura y la vida util las declaras tu y constan en el (`CHN-30`, y `CHN-87`: «chocolate», «cacao», «bombon» y «confiteria» aparecen 0 veces en todo el RD 1021/2022). Los alergenos pueden ir en cartel (`CHN-89`) y el lote tiene tres vias de exencion (`CHN-36`).</v>
+        <v>Se despacha a granel en la vitrina, sin etiqueta. Entonces la referencia NO es el art. 4.2: es TU sistema de autocontrol, y la temperatura y la vida útil las declaras tu y constan en el (`CHN-30`, y `CHN-87`: «chocolate», «cacao», «bombón» y «confitería» aparecen 0 veces en todo el RD 1021/2022). Los alérgenos pueden ir en cartel (`CHN-89`) y el lote tiene tres vías de exención (`CHN-36`).</v>
       </c>
       <c r="F22" t="str">
         <f>IF($C22=$A$7,$F$7,IF($C22=$A$8,$F$8,""))</f>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Bombon de praline de cacahuete</t>
+          <t>Bombón de praline de cacahuete</t>
         </is>
       </c>
       <c r="C23" s="14" t="inlineStr">
@@ -5205,7 +5205,7 @@
       </c>
       <c r="E23" t="str">
         <f>IF($C23=$A$8,$B$8,"")</f>
-        <v>Se despacha a granel en la vitrina, sin etiqueta. Entonces la referencia NO es el art. 4.2: es TU sistema de autocontrol, y la temperatura y la vida util las declaras tu y constan en el (`CHN-30`, y `CHN-87`: «chocolate», «cacao», «bombon» y «confiteria» aparecen 0 veces en todo el RD 1021/2022). Los alergenos pueden ir en cartel (`CHN-89`) y el lote tiene tres vias de exencion (`CHN-36`).</v>
+        <v>Se despacha a granel en la vitrina, sin etiqueta. Entonces la referencia NO es el art. 4.2: es TU sistema de autocontrol, y la temperatura y la vida útil las declaras tu y constan en el (`CHN-30`, y `CHN-87`: «chocolate», «cacao», «bombón» y «confitería» aparecen 0 veces en todo el RD 1021/2022). Los alérgenos pueden ir en cartel (`CHN-89`) y el lote tiene tres vías de exención (`CHN-36`).</v>
       </c>
       <c r="F23" t="str">
         <f>IF($C23=$A$7,$F$7,IF($C23=$A$8,$F$8,""))</f>
@@ -5232,7 +5232,7 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Bombon crujiente de sesamo y barquillo</t>
+          <t>Bombón crujiente de sesamo y barquillo</t>
         </is>
       </c>
       <c r="C24" s="14" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E24" t="str">
         <f>IF($C24=$A$8,$B$8,"")</f>
-        <v>Se despacha a granel en la vitrina, sin etiqueta. Entonces la referencia NO es el art. 4.2: es TU sistema de autocontrol, y la temperatura y la vida util las declaras tu y constan en el (`CHN-30`, y `CHN-87`: «chocolate», «cacao», «bombon» y «confiteria» aparecen 0 veces en todo el RD 1021/2022). Los alergenos pueden ir en cartel (`CHN-89`) y el lote tiene tres vias de exencion (`CHN-36`).</v>
+        <v>Se despacha a granel en la vitrina, sin etiqueta. Entonces la referencia NO es el art. 4.2: es TU sistema de autocontrol, y la temperatura y la vida útil las declaras tu y constan en el (`CHN-30`, y `CHN-87`: «chocolate», «cacao», «bombón» y «confitería» aparecen 0 veces en todo el RD 1021/2022). Los alérgenos pueden ir en cartel (`CHN-89`) y el lote tiene tres vías de exención (`CHN-36`).</v>
       </c>
       <c r="F24" t="str">
         <f>IF($C24=$A$7,$F$7,IF($C24=$A$8,$F$8,""))</f>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Bombon de naranja confitada y chocolate negro</t>
+          <t>Bombón de naranja confitada y chocolate negro</t>
         </is>
       </c>
       <c r="C25" s="14" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="E25" t="str">
         <f>IF($C25=$A$8,$B$8,"")</f>
-        <v>Se despacha a granel en la vitrina, sin etiqueta. Entonces la referencia NO es el art. 4.2: es TU sistema de autocontrol, y la temperatura y la vida util las declaras tu y constan en el (`CHN-30`, y `CHN-87`: «chocolate», «cacao», «bombon» y «confiteria» aparecen 0 veces en todo el RD 1021/2022). Los alergenos pueden ir en cartel (`CHN-89`) y el lote tiene tres vias de exencion (`CHN-36`).</v>
+        <v>Se despacha a granel en la vitrina, sin etiqueta. Entonces la referencia NO es el art. 4.2: es TU sistema de autocontrol, y la temperatura y la vida útil las declaras tu y constan en el (`CHN-30`, y `CHN-87`: «chocolate», «cacao», «bombón» y «confitería» aparecen 0 veces en todo el RD 1021/2022). Los alérgenos pueden ir en cartel (`CHN-89`) y el lote tiene tres vías de exención (`CHN-36`).</v>
       </c>
       <c r="F25" t="str">
         <f>IF($C25=$A$7,$F$7,IF($C25=$A$8,$F$8,""))</f>
@@ -5324,7 +5324,7 @@
       </c>
       <c r="D26" t="str">
         <f>IF($C26=$A$7,$B$7,"")</f>
-        <v>Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservacion POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran ademas las doce menciones del art. 9.1 del Rgto. 1169/2011 (`CHN-35`) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (`CHN-36`).</v>
+        <v>Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservación POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran además las doce menciones del art. 9.1 del Rgto. 1169/2011 (`CHN-35`) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (`CHN-36`).</v>
       </c>
       <c r="E26">
         <f>IF($C26=$A$8,$B$8,"")</f>
@@ -5365,7 +5365,7 @@
       </c>
       <c r="D27" t="str">
         <f>IF($C27=$A$7,$B$7,"")</f>
-        <v>Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservacion POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran ademas las doce menciones del art. 9.1 del Rgto. 1169/2011 (`CHN-35`) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (`CHN-36`).</v>
+        <v>Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservación POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran además las doce menciones del art. 9.1 del Rgto. 1169/2011 (`CHN-35`) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (`CHN-36`).</v>
       </c>
       <c r="E27">
         <f>IF($C27=$A$8,$B$8,"")</f>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="D28" t="str">
         <f>IF($C28=$A$7,$B$7,"")</f>
-        <v>Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservacion POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran ademas las doce menciones del art. 9.1 del Rgto. 1169/2011 (`CHN-35`) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (`CHN-36`).</v>
+        <v>Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservación POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran además las doce menciones del art. 9.1 del Rgto. 1169/2011 (`CHN-35`) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (`CHN-36`).</v>
       </c>
       <c r="E28">
         <f>IF($C28=$A$8,$B$8,"")</f>
@@ -5447,7 +5447,7 @@
       </c>
       <c r="D29" t="str">
         <f>IF($C29=$A$7,$B$7,"")</f>
-        <v>Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservacion POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran ademas las doce menciones del art. 9.1 del Rgto. 1169/2011 (`CHN-35`) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (`CHN-36`).</v>
+        <v>Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservación POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran además las doce menciones del art. 9.1 del Rgto. 1169/2011 (`CHN-35`) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (`CHN-36`).</v>
       </c>
       <c r="E29">
         <f>IF($C29=$A$8,$B$8,"")</f>
@@ -5488,7 +5488,7 @@
       </c>
       <c r="D30" t="str">
         <f>IF($C30=$A$7,$B$7,"")</f>
-        <v>Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservacion POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran ademas las doce menciones del art. 9.1 del Rgto. 1169/2011 (`CHN-35`) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (`CHN-36`).</v>
+        <v>Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservación POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran además las doce menciones del art. 9.1 del Rgto. 1169/2011 (`CHN-35`) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (`CHN-36`).</v>
       </c>
       <c r="E30">
         <f>IF($C30=$A$8,$B$8,"")</f>
@@ -5529,7 +5529,7 @@
       </c>
       <c r="D31" t="str">
         <f>IF($C31=$A$7,$B$7,"")</f>
-        <v>Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservacion POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran ademas las doce menciones del art. 9.1 del Rgto. 1169/2011 (`CHN-35`) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (`CHN-36`).</v>
+        <v>Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservación POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran además las doce menciones del art. 9.1 del Rgto. 1169/2011 (`CHN-35`) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (`CHN-36`).</v>
       </c>
       <c r="E31">
         <f>IF($C31=$A$8,$B$8,"")</f>
@@ -5570,7 +5570,7 @@
       </c>
       <c r="D32" t="str">
         <f>IF($C32=$A$7,$B$7,"")</f>
-        <v>Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservacion POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran ademas las doce menciones del art. 9.1 del Rgto. 1169/2011 (`CHN-35`) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (`CHN-36`).</v>
+        <v>Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservación POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran además las doce menciones del art. 9.1 del Rgto. 1169/2011 (`CHN-35`) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (`CHN-36`).</v>
       </c>
       <c r="E32">
         <f>IF($C32=$A$8,$B$8,"")</f>
@@ -5611,7 +5611,7 @@
       </c>
       <c r="D33" t="str">
         <f>IF($C33=$A$7,$B$7,"")</f>
-        <v>Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservacion POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran ademas las doce menciones del art. 9.1 del Rgto. 1169/2011 (`CHN-35`) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (`CHN-36`).</v>
+        <v>Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservación POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran además las doce menciones del art. 9.1 del Rgto. 1169/2011 (`CHN-35`) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (`CHN-36`).</v>
       </c>
       <c r="E33">
         <f>IF($C33=$A$8,$B$8,"")</f>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="E34" t="str">
         <f>IF($C34=$A$8,$B$8,"")</f>
-        <v>Se despacha a granel en la vitrina, sin etiqueta. Entonces la referencia NO es el art. 4.2: es TU sistema de autocontrol, y la temperatura y la vida util las declaras tu y constan en el (`CHN-30`, y `CHN-87`: «chocolate», «cacao», «bombon» y «confiteria» aparecen 0 veces en todo el RD 1021/2022). Los alergenos pueden ir en cartel (`CHN-89`) y el lote tiene tres vias de exencion (`CHN-36`).</v>
+        <v>Se despacha a granel en la vitrina, sin etiqueta. Entonces la referencia NO es el art. 4.2: es TU sistema de autocontrol, y la temperatura y la vida útil las declaras tu y constan en el (`CHN-30`, y `CHN-87`: «chocolate», «cacao», «bombón» y «confitería» aparecen 0 veces en todo el RD 1021/2022). Los alérgenos pueden ir en cartel (`CHN-89`) y el lote tiene tres vías de exención (`CHN-36`).</v>
       </c>
       <c r="F34" t="str">
         <f>IF($C34=$A$7,$F$7,IF($C34=$A$8,$F$8,""))</f>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="D35" t="str">
         <f>IF($C35=$A$7,$B$7,"")</f>
-        <v>Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservacion POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran ademas las doce menciones del art. 9.1 del Rgto. 1169/2011 (`CHN-35`) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (`CHN-36`).</v>
+        <v>Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservación POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran además las doce menciones del art. 9.1 del Rgto. 1169/2011 (`CHN-35`) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (`CHN-36`).</v>
       </c>
       <c r="E35">
         <f>IF($C35=$A$8,$B$8,"")</f>
@@ -5734,7 +5734,7 @@
       </c>
       <c r="D36" t="str">
         <f>IF($C36=$A$7,$B$7,"")</f>
-        <v>Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservacion POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran ademas las doce menciones del art. 9.1 del Rgto. 1169/2011 (`CHN-35`) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (`CHN-36`).</v>
+        <v>Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservación POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran además las doce menciones del art. 9.1 del Rgto. 1169/2011 (`CHN-35`) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (`CHN-36`).</v>
       </c>
       <c r="E36">
         <f>IF($C36=$A$8,$B$8,"")</f>
@@ -5779,7 +5779,7 @@
       </c>
       <c r="E37" t="str">
         <f>IF($C37=$A$8,$B$8,"")</f>
-        <v>Se despacha a granel en la vitrina, sin etiqueta. Entonces la referencia NO es el art. 4.2: es TU sistema de autocontrol, y la temperatura y la vida util las declaras tu y constan en el (`CHN-30`, y `CHN-87`: «chocolate», «cacao», «bombon» y «confiteria» aparecen 0 veces en todo el RD 1021/2022). Los alergenos pueden ir en cartel (`CHN-89`) y el lote tiene tres vias de exencion (`CHN-36`).</v>
+        <v>Se despacha a granel en la vitrina, sin etiqueta. Entonces la referencia NO es el art. 4.2: es TU sistema de autocontrol, y la temperatura y la vida útil las declaras tu y constan en el (`CHN-30`, y `CHN-87`: «chocolate», «cacao», «bombón» y «confitería» aparecen 0 veces en todo el RD 1021/2022). Los alérgenos pueden ir en cartel (`CHN-89`) y el lote tiene tres vías de exención (`CHN-36`).</v>
       </c>
       <c r="F37" t="str">
         <f>IF($C37=$A$7,$F$7,IF($C37=$A$8,$F$8,""))</f>
@@ -5806,7 +5806,7 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Turron de chocolate con almendra, 250 g</t>
+          <t>Turrón de chocolate con almendra, 250 g</t>
         </is>
       </c>
       <c r="C38" s="14" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="D38" t="str">
         <f>IF($C38=$A$7,$B$7,"")</f>
-        <v>Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservacion POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran ademas las doce menciones del art. 9.1 del Rgto. 1169/2011 (`CHN-35`) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (`CHN-36`).</v>
+        <v>Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservación POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran además las doce menciones del art. 9.1 del Rgto. 1169/2011 (`CHN-35`) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (`CHN-36`).</v>
       </c>
       <c r="E38">
         <f>IF($C38=$A$8,$B$8,"")</f>
@@ -5857,7 +5857,7 @@
       </c>
       <c r="D39" t="str">
         <f>IF($C39=$A$7,$B$7,"")</f>
-        <v>Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservacion POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran ademas las doce menciones del art. 9.1 del Rgto. 1169/2011 (`CHN-35`) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (`CHN-36`).</v>
+        <v>Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservación POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran además las doce menciones del art. 9.1 del Rgto. 1169/2011 (`CHN-35`) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (`CHN-36`).</v>
       </c>
       <c r="E39">
         <f>IF($C39=$A$8,$B$8,"")</f>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="D40" t="str">
         <f>IF($C40=$A$7,$B$7,"")</f>
-        <v>Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservacion POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran ademas las doce menciones del art. 9.1 del Rgto. 1169/2011 (`CHN-35`) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (`CHN-36`).</v>
+        <v>Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservación POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran además las doce menciones del art. 9.1 del Rgto. 1169/2011 (`CHN-35`) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (`CHN-36`).</v>
       </c>
       <c r="E40">
         <f>IF($C40=$A$8,$B$8,"")</f>
@@ -5939,7 +5939,7 @@
       </c>
       <c r="D41" t="str">
         <f>IF($C41=$A$7,$B$7,"")</f>
-        <v>Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservacion POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran ademas las doce menciones del art. 9.1 del Rgto. 1169/2011 (`CHN-35`) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (`CHN-36`).</v>
+        <v>Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservación POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran además las doce menciones del art. 9.1 del Rgto. 1169/2011 (`CHN-35`) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (`CHN-36`).</v>
       </c>
       <c r="E41">
         <f>IF($C41=$A$8,$B$8,"")</f>
@@ -5980,7 +5980,7 @@
       </c>
       <c r="D42" t="str">
         <f>IF($C42=$A$7,$B$7,"")</f>
-        <v>Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservacion POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran ademas las doce menciones del art. 9.1 del Rgto. 1169/2011 (`CHN-35`) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (`CHN-36`).</v>
+        <v>Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservación POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran además las doce menciones del art. 9.1 del Rgto. 1169/2011 (`CHN-35`) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (`CHN-36`).</v>
       </c>
       <c r="E42">
         <f>IF($C42=$A$8,$B$8,"")</f>
@@ -6021,7 +6021,7 @@
       </c>
       <c r="D43" t="str">
         <f>IF($C43=$A$7,$B$7,"")</f>
-        <v>Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservacion POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran ademas las doce menciones del art. 9.1 del Rgto. 1169/2011 (`CHN-35`) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (`CHN-36`).</v>
+        <v>Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservación POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran además las doce menciones del art. 9.1 del Rgto. 1169/2011 (`CHN-35`) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (`CHN-36`).</v>
       </c>
       <c r="E43">
         <f>IF($C43=$A$8,$B$8,"")</f>
@@ -6185,7 +6185,7 @@
     <row r="3" ht="26" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Las cinco temperaturas del kit, el rango de trabajo de TU vitrina y la que declaras para cada referencia. El semáforo sólo se enciende por encima de 20 grados C.</t>
+          <t>Las cinco temperaturas del kit, el rango de trabajo de TU vitrina y la que declaras para cada referencia. El semáforo sólo se enciende por encima de 20 °C.</t>
         </is>
       </c>
     </row>
@@ -6232,7 +6232,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>18 a 20 grados C</t>
+          <t>18 a 20 °C</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -6247,19 +6247,19 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Verificar la temperatura y la humedad del obrador: objetivo 18-20 grados C y 50-60 %</t>
+          <t>Verificar la temperatura y la humedad del obrador: objetivo 18-20 °C y 50-60 %</t>
         </is>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Camara de conservacion de chocolate</t>
+          <t>Cámara de conservación de chocolate</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>15 a 18 grados C</t>
+          <t>15 a 18 °C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -6274,7 +6274,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>Comprobar que la camara de conservacion ha funcionado toda la noche (sin cortes ni alarmas) y registrar la temperatura: objetivo 15-18 grados C y 50-60 % de humedad</t>
+          <t>Comprobar que la cámara de conservación ha funcionado toda la noche (sin cortes ni alarmas) y registrar la temperatura: objetivo 15-18 °C y 50-60 % de humedad</t>
         </is>
       </c>
     </row>
@@ -6286,7 +6286,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0 a 4 grados C</t>
+          <t>0 a 4 °C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Comprobar que la nevera de rellenos y ganaches ha funcionado toda la noche y registrar la temperatura: objetivo 0-4 grados C</t>
+          <t>Comprobar que la nevera de rellenos y ganaches ha funcionado toda la noche y registrar la temperatura: objetivo 0-4 °C</t>
         </is>
       </c>
     </row>
@@ -6313,7 +6313,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>20 a 22 grados C</t>
+          <t>20 a 22 °C</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -6328,19 +6328,19 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>Encender aire acondicionado - mantener sala 20-22 grados C</t>
+          <t>Encender aire acondicionado - mantener sala 20-22 °C</t>
         </is>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Vitrina de bomboneria</t>
+          <t>Vitrina de bombonería</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>16 a 18 grados C</t>
+          <t>16 a 18 °C</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -6355,14 +6355,14 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Comprobar que las vitrinas temperadas han alcanzado 16-18 grados C y menos del 55 % de humedad antes de montar el genero</t>
+          <t>Comprobar que las vitrinas temperadas han alcanzado 16-18 °C y menos del 55 % de humedad antes de montar el genero</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Confundir la temperatura de la SALA con la de la CÁMARA es uno de los errores que más caro salen: son dos cosas distintas y conviven en el mismo local. Y la nevera de 0-4 grados C es la del RELLENO, no la del bombón acabado: el chocolate terminado no va a esa temperatura, condensa.</t>
+          <t>Confundir la temperatura de la SALA con la de la CÁMARA es uno de los errores que más caro salen: son dos cosas distintas y conviven en el mismo local. Y la nevera de 0-4 °C es la del RELLENO, no la del bombón acabado: el chocolate terminado no va a esa temperatura, condensa.</t>
         </is>
       </c>
     </row>
@@ -6415,7 +6415,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>El objetivo operativo del kit para la vitrina es 16-18 grados C con menos del 55 % de humedad, y es lo que viene puesto. El RANGO DE TRABAJO del equipo es otra cosa: una vitrina de bombonería real trabaja, por ejemplo, entre +14 y +17 grados C. Pon el de la tuya, que viene en su ficha técnica. El semáforo no se enciende por estar en 16-18: sólo por pasar de 20.</t>
+          <t>El objetivo operativo del kit para la vitrina es 16-18 grados C con menos del 55 % de humedad, y es lo que viene puesto. El RANGO DE TRABAJO del equipo es otra cosa: una vitrina de bombonería real trabaja, por ejemplo, entre +14 y +17 °C. Pon el de la tuya, que viene en su ficha técnica. El semáforo no se enciende por estar en 16-18: sólo por pasar de 20.</t>
         </is>
       </c>
     </row>
@@ -6541,7 +6541,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Bombon de ganache de chocolate negro 70 %</t>
+          <t>Bombón de ganache de chocolate negro 70 %</t>
         </is>
       </c>
       <c r="C22" t="str">
@@ -6584,7 +6584,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Bombon de ganache de leche y vainilla</t>
+          <t>Bombón de ganache de leche y vainilla</t>
         </is>
       </c>
       <c r="C23" t="str">
@@ -6627,7 +6627,7 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Bombon de praline de avellana</t>
+          <t>Bombón de praline de avellana</t>
         </is>
       </c>
       <c r="C24" t="str">
@@ -6670,7 +6670,7 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Bombon de gianduja de avellana</t>
+          <t>Bombón de gianduja de avellana</t>
         </is>
       </c>
       <c r="C25" t="str">
@@ -6756,7 +6756,7 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>Bombon de licor de ron</t>
+          <t>Bombón de licor de ron</t>
         </is>
       </c>
       <c r="C27" t="str">
@@ -6799,7 +6799,7 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Bombon de caramelo salado</t>
+          <t>Bombón de caramelo salado</t>
         </is>
       </c>
       <c r="C28" t="str">
@@ -6842,7 +6842,7 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Bombon de praline de cacahuete</t>
+          <t>Bombón de praline de cacahuete</t>
         </is>
       </c>
       <c r="C29" t="str">
@@ -6885,7 +6885,7 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Bombon crujiente de sesamo y barquillo</t>
+          <t>Bombón crujiente de sesamo y barquillo</t>
         </is>
       </c>
       <c r="C30" t="str">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Bombon de naranja confitada y chocolate negro</t>
+          <t>Bombón de naranja confitada y chocolate negro</t>
         </is>
       </c>
       <c r="C31" t="str">
@@ -7487,7 +7487,7 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>Turron de chocolate con almendra, 250 g</t>
+          <t>Turrón de chocolate con almendra, 250 g</t>
         </is>
       </c>
       <c r="C44" t="str">
@@ -7745,7 +7745,7 @@
       </c>
       <c r="B50" s="15" t="inlineStr">
         <is>
-          <t>Referencias por encima de la alarma de 20 grados C</t>
+          <t>Referencias por encima de la alarma de 20 °C</t>
         </is>
       </c>
       <c r="D50" s="16">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Bombon de ganache de chocolate negro 70 %</t>
+          <t>Bombón de ganache de chocolate negro 70 %</t>
         </is>
       </c>
       <c r="C16" s="9" t="n">
@@ -8058,7 +8058,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Bombon de ganache de leche y vainilla</t>
+          <t>Bombón de ganache de leche y vainilla</t>
         </is>
       </c>
       <c r="C17" s="9" t="n">
@@ -8131,7 +8131,7 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Bombon de praline de avellana</t>
+          <t>Bombón de praline de avellana</t>
         </is>
       </c>
       <c r="C18" s="9" t="n">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Bombon de gianduja de avellana</t>
+          <t>Bombón de gianduja de avellana</t>
         </is>
       </c>
       <c r="C19" s="9" t="n">
@@ -8350,7 +8350,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Bombon de licor de ron</t>
+          <t>Bombón de licor de ron</t>
         </is>
       </c>
       <c r="C21" s="9" t="n">
@@ -8423,7 +8423,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Bombon de caramelo salado</t>
+          <t>Bombón de caramelo salado</t>
         </is>
       </c>
       <c r="C22" s="9" t="n">
@@ -8496,7 +8496,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Bombon de praline de cacahuete</t>
+          <t>Bombón de praline de cacahuete</t>
         </is>
       </c>
       <c r="C23" s="9" t="n">
@@ -8569,7 +8569,7 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Bombon crujiente de sesamo y barquillo</t>
+          <t>Bombón crujiente de sesamo y barquillo</t>
         </is>
       </c>
       <c r="C24" s="9" t="n">
@@ -8642,7 +8642,7 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Bombon de naranja confitada y chocolate negro</t>
+          <t>Bombón de naranja confitada y chocolate negro</t>
         </is>
       </c>
       <c r="C25" s="9" t="n">
@@ -9591,7 +9591,7 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Turron de chocolate con almendra, 250 g</t>
+          <t>Turrón de chocolate con almendra, 250 g</t>
         </is>
       </c>
       <c r="C38" s="9" t="n">

--- a/astro-site/public/dl/guia-chocolateria-obrador/vida-util-rellenos-y-rotacion.xlsx
+++ b/astro-site/public/dl/guia-chocolateria-obrador/vida-util-rellenos-y-rotacion.xlsx
@@ -1114,7 +1114,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>grados C</t>
+          <t>°C</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Bombón de praline de avellana</t>
+          <t>Bombón de praliné de avellana</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>Bombones de praline, gianduja y frutos secos</t>
+          <t>Bombones de praliné, gianduja y frutos secos</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>Bombones de praline, gianduja y frutos secos</t>
+          <t>Bombones de praliné, gianduja y frutos secos</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>Vigilar la cristalización del azúcar en la cascara: revienta y gotea</t>
+          <t>Vigilar la cristalización del azúcar en la cáscara: revienta y gotea</t>
         </is>
       </c>
     </row>
@@ -1715,7 +1715,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Bombón de praline de cacahuete</t>
+          <t>Bombón de praliné de cacahuete</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>Bombones de praline, gianduja y frutos secos</t>
+          <t>Bombones de praliné, gianduja y frutos secos</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Bombón crujiente de sesamo y barquillo</t>
+          <t>Bombón crujiente de sésamo y barquillo</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>Crujiente de sesamo y barquillo</t>
+          <t>Crujiente de sésamo y barquillo</t>
         </is>
       </c>
       <c r="E24" s="11" t="n">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>Barquillos y crujientes banados</t>
+          <t>Barquillos y crujientes bañados</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>Frutos secos garrapinados y frutas confitadas banadas</t>
+          <t>Frutos secos garrapiñados y frutas confitadas bañadas</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>Se apelmazan con la humedad; envasado hermetico con desecante si tu obrador es humedo</t>
+          <t>Se apelmazan con la humedad; envasado hermético con desecante si tu obrador es húmedo</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Tableta rellena de praline, 100 g</t>
+          <t>Tableta rellena de praliné, 100 g</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>Bombones de praline, gianduja y frutos secos</t>
+          <t>Bombones de praliné, gianduja y frutos secos</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2401,7 +2401,7 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>Hueso de santo banado en chocolate</t>
+          <t>Hueso de santo bañado en chocolate</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>Almendras marcona banadas en chocolate, bolsa de 150 g</t>
+          <t>Almendras marcona bañadas en chocolate, bolsa de 150 g</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>Frutos secos garrapinados y frutas confitadas banadas</t>
+          <t>Frutos secos garrapiñados y frutas confitadas bañadas</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
-          <t>Se apelmazan con la humedad; envasado hermetico con desecante si tu obrador es humedo</t>
+          <t>Se apelmazan con la humedad; envasado hermético con desecante si tu obrador es húmedo</t>
         </is>
       </c>
     </row>
@@ -3084,12 +3084,12 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Bombón de praline de avellana</t>
+          <t>Bombón de praliné de avellana</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Bombones de praline, gianduja y frutos secos</t>
+          <t>Bombones de praliné, gianduja y frutos secos</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Bombones de praline, gianduja y frutos secos</t>
+          <t>Bombones de praliné, gianduja y frutos secos</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3339,12 +3339,12 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Bombón de praline de cacahuete</t>
+          <t>Bombón de praliné de cacahuete</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Bombones de praline, gianduja y frutos secos</t>
+          <t>Bombones de praliné, gianduja y frutos secos</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3390,12 +3390,12 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Bombón crujiente de sesamo y barquillo</t>
+          <t>Bombón crujiente de sésamo y barquillo</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Barquillos y crujientes banados</t>
+          <t>Barquillos y crujientes bañados</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Frutos secos garrapinados y frutas confitadas banadas</t>
+          <t>Frutos secos garrapiñados y frutas confitadas bañadas</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Tableta rellena de praline, 100 g</t>
+          <t>Tableta rellena de praliné, 100 g</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>Bombones de praline, gianduja y frutos secos</t>
+          <t>Bombones de praliné, gianduja y frutos secos</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4053,7 +4053,7 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>Hueso de santo banado en chocolate</t>
+          <t>Hueso de santo bañado en chocolate</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
@@ -4155,12 +4155,12 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>Almendras marcona banadas en chocolate, bolsa de 150 g</t>
+          <t>Almendras marcona bañadas en chocolate, bolsa de 150 g</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>Frutos secos garrapinados y frutas confitadas banadas</t>
+          <t>Frutos secos garrapiñados y frutas confitadas bañadas</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -4539,7 +4539,7 @@
     <row r="52" ht="28" customHeight="1">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>Bombones de praline, gianduja y frutos secos</t>
+          <t>Bombones de praliné, gianduja y frutos secos</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4583,14 +4583,14 @@
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>Vigilar la cristalización del azúcar en la cascara: revienta y gotea</t>
+          <t>Vigilar la cristalización del azúcar en la cáscara: revienta y gotea</t>
         </is>
       </c>
     </row>
     <row r="55" ht="28" customHeight="1">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>Frutos secos garrapinados y frutas confitadas banadas</t>
+          <t>Frutos secos garrapiñados y frutas confitadas bañadas</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -4600,14 +4600,14 @@
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>Se apelmazan con la humedad; envasado hermetico con desecante si tu obrador es humedo</t>
+          <t>Se apelmazan con la humedad; envasado hermético con desecante si tu obrador es húmedo</t>
         </is>
       </c>
     </row>
     <row r="56" ht="28" customHeight="1">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>Barquillos y crujientes banados</t>
+          <t>Barquillos y crujientes bañados</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -4805,7 +4805,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservación POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran además las doce menciones del art. 9.1 del Rgto. 1169/2011 (`CHN-35`) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (`CHN-36`).</t>
+          <t>Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservación POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran además las doce menciones del art. 9.1 del Rgto. 1169/2011 (CHN-35) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (CHN-36).</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Se despacha a granel en la vitrina, sin etiqueta. Entonces la referencia NO es el art. 4.2: es TU sistema de autocontrol, y la temperatura y la vida útil las declaras tu y constan en el (`CHN-30`, y `CHN-87`: «chocolate», «cacao», «bombón» y «confitería» aparecen 0 veces en todo el RD 1021/2022). Los alérgenos pueden ir en cartel (`CHN-89`) y el lote tiene tres vías de exención (`CHN-36`).</t>
+          <t>Se despacha a granel en la vitrina, sin etiqueta. Entonces la referencia NO es el art. 4.2: es TU sistema de autocontrol, y la temperatura y la vida útil las declaras tu y constan en el (CHN-30, y CHN-87: «chocolate», «cacao», «bombón» y «confitería» aparecen 0 veces en todo el RD 1021/2022). Los alérgenos pueden ir en cartel (CHN-89) y el lote tiene tres vías de exención (CHN-36).</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="E16" t="str">
         <f>IF($C16=$A$8,$B$8,"")</f>
-        <v>Se despacha a granel en la vitrina, sin etiqueta. Entonces la referencia NO es el art. 4.2: es TU sistema de autocontrol, y la temperatura y la vida útil las declaras tu y constan en el (`CHN-30`, y `CHN-87`: «chocolate», «cacao», «bombón» y «confitería» aparecen 0 veces en todo el RD 1021/2022). Los alérgenos pueden ir en cartel (`CHN-89`) y el lote tiene tres vías de exención (`CHN-36`).</v>
+        <v>Se despacha a granel en la vitrina, sin etiqueta. Entonces la referencia NO es el art. 4.2: es TU sistema de autocontrol, y la temperatura y la vida útil las declaras tu y constan en el (CHN-30, y CHN-87: «chocolate», «cacao», «bombón» y «confitería» aparecen 0 veces en todo el RD 1021/2022). Los alérgenos pueden ir en cartel (CHN-89) y el lote tiene tres vías de exención (CHN-36).</v>
       </c>
       <c r="F16" t="str">
         <f>IF($C16=$A$7,$F$7,IF($C16=$A$8,$F$8,""))</f>
@@ -4959,7 +4959,7 @@
       </c>
       <c r="E17" t="str">
         <f>IF($C17=$A$8,$B$8,"")</f>
-        <v>Se despacha a granel en la vitrina, sin etiqueta. Entonces la referencia NO es el art. 4.2: es TU sistema de autocontrol, y la temperatura y la vida útil las declaras tu y constan en el (`CHN-30`, y `CHN-87`: «chocolate», «cacao», «bombón» y «confitería» aparecen 0 veces en todo el RD 1021/2022). Los alérgenos pueden ir en cartel (`CHN-89`) y el lote tiene tres vías de exención (`CHN-36`).</v>
+        <v>Se despacha a granel en la vitrina, sin etiqueta. Entonces la referencia NO es el art. 4.2: es TU sistema de autocontrol, y la temperatura y la vida útil las declaras tu y constan en el (CHN-30, y CHN-87: «chocolate», «cacao», «bombón» y «confitería» aparecen 0 veces en todo el RD 1021/2022). Los alérgenos pueden ir en cartel (CHN-89) y el lote tiene tres vías de exención (CHN-36).</v>
       </c>
       <c r="F17" t="str">
         <f>IF($C17=$A$7,$F$7,IF($C17=$A$8,$F$8,""))</f>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Bombón de praline de avellana</t>
+          <t>Bombón de praliné de avellana</t>
         </is>
       </c>
       <c r="C18" s="14" t="inlineStr">
@@ -5000,7 +5000,7 @@
       </c>
       <c r="E18" t="str">
         <f>IF($C18=$A$8,$B$8,"")</f>
-        <v>Se despacha a granel en la vitrina, sin etiqueta. Entonces la referencia NO es el art. 4.2: es TU sistema de autocontrol, y la temperatura y la vida útil las declaras tu y constan en el (`CHN-30`, y `CHN-87`: «chocolate», «cacao», «bombón» y «confitería» aparecen 0 veces en todo el RD 1021/2022). Los alérgenos pueden ir en cartel (`CHN-89`) y el lote tiene tres vías de exención (`CHN-36`).</v>
+        <v>Se despacha a granel en la vitrina, sin etiqueta. Entonces la referencia NO es el art. 4.2: es TU sistema de autocontrol, y la temperatura y la vida útil las declaras tu y constan en el (CHN-30, y CHN-87: «chocolate», «cacao», «bombón» y «confitería» aparecen 0 veces en todo el RD 1021/2022). Los alérgenos pueden ir en cartel (CHN-89) y el lote tiene tres vías de exención (CHN-36).</v>
       </c>
       <c r="F18" t="str">
         <f>IF($C18=$A$7,$F$7,IF($C18=$A$8,$F$8,""))</f>
@@ -5041,7 +5041,7 @@
       </c>
       <c r="E19" t="str">
         <f>IF($C19=$A$8,$B$8,"")</f>
-        <v>Se despacha a granel en la vitrina, sin etiqueta. Entonces la referencia NO es el art. 4.2: es TU sistema de autocontrol, y la temperatura y la vida útil las declaras tu y constan en el (`CHN-30`, y `CHN-87`: «chocolate», «cacao», «bombón» y «confitería» aparecen 0 veces en todo el RD 1021/2022). Los alérgenos pueden ir en cartel (`CHN-89`) y el lote tiene tres vías de exención (`CHN-36`).</v>
+        <v>Se despacha a granel en la vitrina, sin etiqueta. Entonces la referencia NO es el art. 4.2: es TU sistema de autocontrol, y la temperatura y la vida útil las declaras tu y constan en el (CHN-30, y CHN-87: «chocolate», «cacao», «bombón» y «confitería» aparecen 0 veces en todo el RD 1021/2022). Los alérgenos pueden ir en cartel (CHN-89) y el lote tiene tres vías de exención (CHN-36).</v>
       </c>
       <c r="F19" t="str">
         <f>IF($C19=$A$7,$F$7,IF($C19=$A$8,$F$8,""))</f>
@@ -5082,7 +5082,7 @@
       </c>
       <c r="E20" t="str">
         <f>IF($C20=$A$8,$B$8,"")</f>
-        <v>Se despacha a granel en la vitrina, sin etiqueta. Entonces la referencia NO es el art. 4.2: es TU sistema de autocontrol, y la temperatura y la vida útil las declaras tu y constan en el (`CHN-30`, y `CHN-87`: «chocolate», «cacao», «bombón» y «confitería» aparecen 0 veces en todo el RD 1021/2022). Los alérgenos pueden ir en cartel (`CHN-89`) y el lote tiene tres vías de exención (`CHN-36`).</v>
+        <v>Se despacha a granel en la vitrina, sin etiqueta. Entonces la referencia NO es el art. 4.2: es TU sistema de autocontrol, y la temperatura y la vida útil las declaras tu y constan en el (CHN-30, y CHN-87: «chocolate», «cacao», «bombón» y «confitería» aparecen 0 veces en todo el RD 1021/2022). Los alérgenos pueden ir en cartel (CHN-89) y el lote tiene tres vías de exención (CHN-36).</v>
       </c>
       <c r="F20" t="str">
         <f>IF($C20=$A$7,$F$7,IF($C20=$A$8,$F$8,""))</f>
@@ -5123,7 +5123,7 @@
       </c>
       <c r="E21" t="str">
         <f>IF($C21=$A$8,$B$8,"")</f>
-        <v>Se despacha a granel en la vitrina, sin etiqueta. Entonces la referencia NO es el art. 4.2: es TU sistema de autocontrol, y la temperatura y la vida útil las declaras tu y constan en el (`CHN-30`, y `CHN-87`: «chocolate», «cacao», «bombón» y «confitería» aparecen 0 veces en todo el RD 1021/2022). Los alérgenos pueden ir en cartel (`CHN-89`) y el lote tiene tres vías de exención (`CHN-36`).</v>
+        <v>Se despacha a granel en la vitrina, sin etiqueta. Entonces la referencia NO es el art. 4.2: es TU sistema de autocontrol, y la temperatura y la vida útil las declaras tu y constan en el (CHN-30, y CHN-87: «chocolate», «cacao», «bombón» y «confitería» aparecen 0 veces en todo el RD 1021/2022). Los alérgenos pueden ir en cartel (CHN-89) y el lote tiene tres vías de exención (CHN-36).</v>
       </c>
       <c r="F21" t="str">
         <f>IF($C21=$A$7,$F$7,IF($C21=$A$8,$F$8,""))</f>
@@ -5164,7 +5164,7 @@
       </c>
       <c r="E22" t="str">
         <f>IF($C22=$A$8,$B$8,"")</f>
-        <v>Se despacha a granel en la vitrina, sin etiqueta. Entonces la referencia NO es el art. 4.2: es TU sistema de autocontrol, y la temperatura y la vida útil las declaras tu y constan en el (`CHN-30`, y `CHN-87`: «chocolate», «cacao», «bombón» y «confitería» aparecen 0 veces en todo el RD 1021/2022). Los alérgenos pueden ir en cartel (`CHN-89`) y el lote tiene tres vías de exención (`CHN-36`).</v>
+        <v>Se despacha a granel en la vitrina, sin etiqueta. Entonces la referencia NO es el art. 4.2: es TU sistema de autocontrol, y la temperatura y la vida útil las declaras tu y constan en el (CHN-30, y CHN-87: «chocolate», «cacao», «bombón» y «confitería» aparecen 0 veces en todo el RD 1021/2022). Los alérgenos pueden ir en cartel (CHN-89) y el lote tiene tres vías de exención (CHN-36).</v>
       </c>
       <c r="F22" t="str">
         <f>IF($C22=$A$7,$F$7,IF($C22=$A$8,$F$8,""))</f>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Bombón de praline de cacahuete</t>
+          <t>Bombón de praliné de cacahuete</t>
         </is>
       </c>
       <c r="C23" s="14" t="inlineStr">
@@ -5205,7 +5205,7 @@
       </c>
       <c r="E23" t="str">
         <f>IF($C23=$A$8,$B$8,"")</f>
-        <v>Se despacha a granel en la vitrina, sin etiqueta. Entonces la referencia NO es el art. 4.2: es TU sistema de autocontrol, y la temperatura y la vida útil las declaras tu y constan en el (`CHN-30`, y `CHN-87`: «chocolate», «cacao», «bombón» y «confitería» aparecen 0 veces en todo el RD 1021/2022). Los alérgenos pueden ir en cartel (`CHN-89`) y el lote tiene tres vías de exención (`CHN-36`).</v>
+        <v>Se despacha a granel en la vitrina, sin etiqueta. Entonces la referencia NO es el art. 4.2: es TU sistema de autocontrol, y la temperatura y la vida útil las declaras tu y constan en el (CHN-30, y CHN-87: «chocolate», «cacao», «bombón» y «confitería» aparecen 0 veces en todo el RD 1021/2022). Los alérgenos pueden ir en cartel (CHN-89) y el lote tiene tres vías de exención (CHN-36).</v>
       </c>
       <c r="F23" t="str">
         <f>IF($C23=$A$7,$F$7,IF($C23=$A$8,$F$8,""))</f>
@@ -5232,7 +5232,7 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Bombón crujiente de sesamo y barquillo</t>
+          <t>Bombón crujiente de sésamo y barquillo</t>
         </is>
       </c>
       <c r="C24" s="14" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E24" t="str">
         <f>IF($C24=$A$8,$B$8,"")</f>
-        <v>Se despacha a granel en la vitrina, sin etiqueta. Entonces la referencia NO es el art. 4.2: es TU sistema de autocontrol, y la temperatura y la vida útil las declaras tu y constan en el (`CHN-30`, y `CHN-87`: «chocolate», «cacao», «bombón» y «confitería» aparecen 0 veces en todo el RD 1021/2022). Los alérgenos pueden ir en cartel (`CHN-89`) y el lote tiene tres vías de exención (`CHN-36`).</v>
+        <v>Se despacha a granel en la vitrina, sin etiqueta. Entonces la referencia NO es el art. 4.2: es TU sistema de autocontrol, y la temperatura y la vida útil las declaras tu y constan en el (CHN-30, y CHN-87: «chocolate», «cacao», «bombón» y «confitería» aparecen 0 veces en todo el RD 1021/2022). Los alérgenos pueden ir en cartel (CHN-89) y el lote tiene tres vías de exención (CHN-36).</v>
       </c>
       <c r="F24" t="str">
         <f>IF($C24=$A$7,$F$7,IF($C24=$A$8,$F$8,""))</f>
@@ -5287,7 +5287,7 @@
       </c>
       <c r="E25" t="str">
         <f>IF($C25=$A$8,$B$8,"")</f>
-        <v>Se despacha a granel en la vitrina, sin etiqueta. Entonces la referencia NO es el art. 4.2: es TU sistema de autocontrol, y la temperatura y la vida útil las declaras tu y constan en el (`CHN-30`, y `CHN-87`: «chocolate», «cacao», «bombón» y «confitería» aparecen 0 veces en todo el RD 1021/2022). Los alérgenos pueden ir en cartel (`CHN-89`) y el lote tiene tres vías de exención (`CHN-36`).</v>
+        <v>Se despacha a granel en la vitrina, sin etiqueta. Entonces la referencia NO es el art. 4.2: es TU sistema de autocontrol, y la temperatura y la vida útil las declaras tu y constan en el (CHN-30, y CHN-87: «chocolate», «cacao», «bombón» y «confitería» aparecen 0 veces en todo el RD 1021/2022). Los alérgenos pueden ir en cartel (CHN-89) y el lote tiene tres vías de exención (CHN-36).</v>
       </c>
       <c r="F25" t="str">
         <f>IF($C25=$A$7,$F$7,IF($C25=$A$8,$F$8,""))</f>
@@ -5324,7 +5324,7 @@
       </c>
       <c r="D26" t="str">
         <f>IF($C26=$A$7,$B$7,"")</f>
-        <v>Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservación POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran además las doce menciones del art. 9.1 del Rgto. 1169/2011 (`CHN-35`) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (`CHN-36`).</v>
+        <v>Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservación POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran además las doce menciones del art. 9.1 del Rgto. 1169/2011 (CHN-35) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (CHN-36).</v>
       </c>
       <c r="E26">
         <f>IF($C26=$A$8,$B$8,"")</f>
@@ -5365,7 +5365,7 @@
       </c>
       <c r="D27" t="str">
         <f>IF($C27=$A$7,$B$7,"")</f>
-        <v>Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservación POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran además las doce menciones del art. 9.1 del Rgto. 1169/2011 (`CHN-35`) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (`CHN-36`).</v>
+        <v>Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservación POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran además las doce menciones del art. 9.1 del Rgto. 1169/2011 (CHN-35) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (CHN-36).</v>
       </c>
       <c r="E27">
         <f>IF($C27=$A$8,$B$8,"")</f>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="D28" t="str">
         <f>IF($C28=$A$7,$B$7,"")</f>
-        <v>Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservación POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran además las doce menciones del art. 9.1 del Rgto. 1169/2011 (`CHN-35`) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (`CHN-36`).</v>
+        <v>Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservación POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran además las doce menciones del art. 9.1 del Rgto. 1169/2011 (CHN-35) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (CHN-36).</v>
       </c>
       <c r="E28">
         <f>IF($C28=$A$8,$B$8,"")</f>
@@ -5447,7 +5447,7 @@
       </c>
       <c r="D29" t="str">
         <f>IF($C29=$A$7,$B$7,"")</f>
-        <v>Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservación POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran además las doce menciones del art. 9.1 del Rgto. 1169/2011 (`CHN-35`) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (`CHN-36`).</v>
+        <v>Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservación POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran además las doce menciones del art. 9.1 del Rgto. 1169/2011 (CHN-35) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (CHN-36).</v>
       </c>
       <c r="E29">
         <f>IF($C29=$A$8,$B$8,"")</f>
@@ -5488,7 +5488,7 @@
       </c>
       <c r="D30" t="str">
         <f>IF($C30=$A$7,$B$7,"")</f>
-        <v>Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservación POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran además las doce menciones del art. 9.1 del Rgto. 1169/2011 (`CHN-35`) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (`CHN-36`).</v>
+        <v>Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservación POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran además las doce menciones del art. 9.1 del Rgto. 1169/2011 (CHN-35) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (CHN-36).</v>
       </c>
       <c r="E30">
         <f>IF($C30=$A$8,$B$8,"")</f>
@@ -5519,7 +5519,7 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Tableta rellena de praline, 100 g</t>
+          <t>Tableta rellena de praliné, 100 g</t>
         </is>
       </c>
       <c r="C31" s="14" t="inlineStr">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="D31" t="str">
         <f>IF($C31=$A$7,$B$7,"")</f>
-        <v>Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservación POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran además las doce menciones del art. 9.1 del Rgto. 1169/2011 (`CHN-35`) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (`CHN-36`).</v>
+        <v>Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservación POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran además las doce menciones del art. 9.1 del Rgto. 1169/2011 (CHN-35) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (CHN-36).</v>
       </c>
       <c r="E31">
         <f>IF($C31=$A$8,$B$8,"")</f>
@@ -5570,7 +5570,7 @@
       </c>
       <c r="D32" t="str">
         <f>IF($C32=$A$7,$B$7,"")</f>
-        <v>Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservación POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran además las doce menciones del art. 9.1 del Rgto. 1169/2011 (`CHN-35`) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (`CHN-36`).</v>
+        <v>Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservación POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran además las doce menciones del art. 9.1 del Rgto. 1169/2011 (CHN-35) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (CHN-36).</v>
       </c>
       <c r="E32">
         <f>IF($C32=$A$8,$B$8,"")</f>
@@ -5611,7 +5611,7 @@
       </c>
       <c r="D33" t="str">
         <f>IF($C33=$A$7,$B$7,"")</f>
-        <v>Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservación POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran además las doce menciones del art. 9.1 del Rgto. 1169/2011 (`CHN-35`) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (`CHN-36`).</v>
+        <v>Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservación POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran además las doce menciones del art. 9.1 del Rgto. 1169/2011 (CHN-35) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (CHN-36).</v>
       </c>
       <c r="E33">
         <f>IF($C33=$A$8,$B$8,"")</f>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="E34" t="str">
         <f>IF($C34=$A$8,$B$8,"")</f>
-        <v>Se despacha a granel en la vitrina, sin etiqueta. Entonces la referencia NO es el art. 4.2: es TU sistema de autocontrol, y la temperatura y la vida útil las declaras tu y constan en el (`CHN-30`, y `CHN-87`: «chocolate», «cacao», «bombón» y «confitería» aparecen 0 veces en todo el RD 1021/2022). Los alérgenos pueden ir en cartel (`CHN-89`) y el lote tiene tres vías de exención (`CHN-36`).</v>
+        <v>Se despacha a granel en la vitrina, sin etiqueta. Entonces la referencia NO es el art. 4.2: es TU sistema de autocontrol, y la temperatura y la vida útil las declaras tu y constan en el (CHN-30, y CHN-87: «chocolate», «cacao», «bombón» y «confitería» aparecen 0 veces en todo el RD 1021/2022). Los alérgenos pueden ir en cartel (CHN-89) y el lote tiene tres vías de exención (CHN-36).</v>
       </c>
       <c r="F34" t="str">
         <f>IF($C34=$A$7,$F$7,IF($C34=$A$8,$F$8,""))</f>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="D35" t="str">
         <f>IF($C35=$A$7,$B$7,"")</f>
-        <v>Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservación POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran además las doce menciones del art. 9.1 del Rgto. 1169/2011 (`CHN-35`) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (`CHN-36`).</v>
+        <v>Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservación POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran además las doce menciones del art. 9.1 del Rgto. 1169/2011 (CHN-35) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (CHN-36).</v>
       </c>
       <c r="E35">
         <f>IF($C35=$A$8,$B$8,"")</f>
@@ -5734,7 +5734,7 @@
       </c>
       <c r="D36" t="str">
         <f>IF($C36=$A$7,$B$7,"")</f>
-        <v>Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservación POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran además las doce menciones del art. 9.1 del Rgto. 1169/2011 (`CHN-35`) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (`CHN-36`).</v>
+        <v>Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservación POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran además las doce menciones del art. 9.1 del Rgto. 1169/2011 (CHN-35) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (CHN-36).</v>
       </c>
       <c r="E36">
         <f>IF($C36=$A$8,$B$8,"")</f>
@@ -5765,7 +5765,7 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>Hueso de santo banado en chocolate</t>
+          <t>Hueso de santo bañado en chocolate</t>
         </is>
       </c>
       <c r="C37" s="14" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="E37" t="str">
         <f>IF($C37=$A$8,$B$8,"")</f>
-        <v>Se despacha a granel en la vitrina, sin etiqueta. Entonces la referencia NO es el art. 4.2: es TU sistema de autocontrol, y la temperatura y la vida útil las declaras tu y constan en el (`CHN-30`, y `CHN-87`: «chocolate», «cacao», «bombón» y «confitería» aparecen 0 veces en todo el RD 1021/2022). Los alérgenos pueden ir en cartel (`CHN-89`) y el lote tiene tres vías de exención (`CHN-36`).</v>
+        <v>Se despacha a granel en la vitrina, sin etiqueta. Entonces la referencia NO es el art. 4.2: es TU sistema de autocontrol, y la temperatura y la vida útil las declaras tu y constan en el (CHN-30, y CHN-87: «chocolate», «cacao», «bombón» y «confitería» aparecen 0 veces en todo el RD 1021/2022). Los alérgenos pueden ir en cartel (CHN-89) y el lote tiene tres vías de exención (CHN-36).</v>
       </c>
       <c r="F37" t="str">
         <f>IF($C37=$A$7,$F$7,IF($C37=$A$8,$F$8,""))</f>
@@ -5816,7 +5816,7 @@
       </c>
       <c r="D38" t="str">
         <f>IF($C38=$A$7,$B$7,"")</f>
-        <v>Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservación POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran además las doce menciones del art. 9.1 del Rgto. 1169/2011 (`CHN-35`) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (`CHN-36`).</v>
+        <v>Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservación POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran además las doce menciones del art. 9.1 del Rgto. 1169/2011 (CHN-35) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (CHN-36).</v>
       </c>
       <c r="E38">
         <f>IF($C38=$A$8,$B$8,"")</f>
@@ -5847,7 +5847,7 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>Almendras marcona banadas en chocolate, bolsa de 150 g</t>
+          <t>Almendras marcona bañadas en chocolate, bolsa de 150 g</t>
         </is>
       </c>
       <c r="C39" s="14" t="inlineStr">
@@ -5857,7 +5857,7 @@
       </c>
       <c r="D39" t="str">
         <f>IF($C39=$A$7,$B$7,"")</f>
-        <v>Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservación POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran además las doce menciones del art. 9.1 del Rgto. 1169/2011 (`CHN-35`) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (`CHN-36`).</v>
+        <v>Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservación POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran además las doce menciones del art. 9.1 del Rgto. 1169/2011 (CHN-35) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (CHN-36).</v>
       </c>
       <c r="E39">
         <f>IF($C39=$A$8,$B$8,"")</f>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="D40" t="str">
         <f>IF($C40=$A$7,$B$7,"")</f>
-        <v>Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservación POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran además las doce menciones del art. 9.1 del Rgto. 1169/2011 (`CHN-35`) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (`CHN-36`).</v>
+        <v>Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservación POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran además las doce menciones del art. 9.1 del Rgto. 1169/2011 (CHN-35) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (CHN-36).</v>
       </c>
       <c r="E40">
         <f>IF($C40=$A$8,$B$8,"")</f>
@@ -5939,7 +5939,7 @@
       </c>
       <c r="D41" t="str">
         <f>IF($C41=$A$7,$B$7,"")</f>
-        <v>Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservación POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran además las doce menciones del art. 9.1 del Rgto. 1169/2011 (`CHN-35`) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (`CHN-36`).</v>
+        <v>Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservación POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran además las doce menciones del art. 9.1 del Rgto. 1169/2011 (CHN-35) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (CHN-36).</v>
       </c>
       <c r="E41">
         <f>IF($C41=$A$8,$B$8,"")</f>
@@ -5980,7 +5980,7 @@
       </c>
       <c r="D42" t="str">
         <f>IF($C42=$A$7,$B$7,"")</f>
-        <v>Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservación POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran además las doce menciones del art. 9.1 del Rgto. 1169/2011 (`CHN-35`) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (`CHN-36`).</v>
+        <v>Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservación POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran además las doce menciones del art. 9.1 del Rgto. 1169/2011 (CHN-35) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (CHN-36).</v>
       </c>
       <c r="E42">
         <f>IF($C42=$A$8,$B$8,"")</f>
@@ -6021,7 +6021,7 @@
       </c>
       <c r="D43" t="str">
         <f>IF($C43=$A$7,$B$7,"")</f>
-        <v>Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservación POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran además las doce menciones del art. 9.1 del Rgto. 1169/2011 (`CHN-35`) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (`CHN-36`).</v>
+        <v>Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservación POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran además las doce menciones del art. 9.1 del Rgto. 1169/2011 (CHN-35) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (CHN-36).</v>
       </c>
       <c r="E43">
         <f>IF($C43=$A$8,$B$8,"")</f>
@@ -6355,7 +6355,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Comprobar que las vitrinas temperadas han alcanzado 16-18 °C y menos del 55 % de humedad antes de montar el genero</t>
+          <t>Comprobar que las vitrinas temperadas han alcanzado 16-18 °C y menos del 55 % de humedad antes de montar el género</t>
         </is>
       </c>
     </row>
@@ -6406,7 +6406,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>grados C</t>
+          <t>°C</t>
         </is>
       </c>
       <c r="F15" t="str">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>grados C</t>
+          <t>°C</t>
         </is>
       </c>
       <c r="F16" t="str">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>grados C</t>
+          <t>°C</t>
         </is>
       </c>
     </row>
@@ -6627,7 +6627,7 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Bombón de praline de avellana</t>
+          <t>Bombón de praliné de avellana</t>
         </is>
       </c>
       <c r="C24" t="str">
@@ -6842,7 +6842,7 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Bombón de praline de cacahuete</t>
+          <t>Bombón de praliné de cacahuete</t>
         </is>
       </c>
       <c r="C29" t="str">
@@ -6885,7 +6885,7 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Bombón crujiente de sesamo y barquillo</t>
+          <t>Bombón crujiente de sésamo y barquillo</t>
         </is>
       </c>
       <c r="C30" t="str">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>Tableta rellena de praline, 100 g</t>
+          <t>Tableta rellena de praliné, 100 g</t>
         </is>
       </c>
       <c r="C37" t="str">
@@ -7444,7 +7444,7 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>Hueso de santo banado en chocolate</t>
+          <t>Hueso de santo bañado en chocolate</t>
         </is>
       </c>
       <c r="C43" t="str">
@@ -7530,7 +7530,7 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>Almendras marcona banadas en chocolate, bolsa de 150 g</t>
+          <t>Almendras marcona bañadas en chocolate, bolsa de 150 g</t>
         </is>
       </c>
       <c r="C45" t="str">
@@ -8131,7 +8131,7 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Bombón de praline de avellana</t>
+          <t>Bombón de praliné de avellana</t>
         </is>
       </c>
       <c r="C18" s="9" t="n">
@@ -8496,7 +8496,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Bombón de praline de cacahuete</t>
+          <t>Bombón de praliné de cacahuete</t>
         </is>
       </c>
       <c r="C23" s="9" t="n">
@@ -8569,7 +8569,7 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Bombón crujiente de sesamo y barquillo</t>
+          <t>Bombón crujiente de sésamo y barquillo</t>
         </is>
       </c>
       <c r="C24" s="9" t="n">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Tableta rellena de praline, 100 g</t>
+          <t>Tableta rellena de praliné, 100 g</t>
         </is>
       </c>
       <c r="C31" s="9" t="n">
@@ -9518,7 +9518,7 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>Hueso de santo banado en chocolate</t>
+          <t>Hueso de santo bañado en chocolate</t>
         </is>
       </c>
       <c r="C37" s="9" t="n">
@@ -9664,7 +9664,7 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>Almendras marcona banadas en chocolate, bolsa de 150 g</t>
+          <t>Almendras marcona bañadas en chocolate, bolsa de 150 g</t>
         </is>
       </c>
       <c r="C39" s="9" t="n">
